--- a/news_daily/2026-10-10.xlsx
+++ b/news_daily/2026-10-10.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,10 +84,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH20"/>
+  <dimension ref="A1:BL20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -518,6 +518,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -821,6 +825,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -856,28 +880,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>重大訴訟</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -917,7 +945,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>MAJOR_LITIGATION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -930,7 +958,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>68ff59bc911c4924bc543e7352b30dad</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>94b9da2b8baf4ad0cc5a2b28</t>
@@ -955,7 +987,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -999,176 +1035,196 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>DUK</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Duke Energy</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2026-10-10T21:09:00+08:00</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Duke Energy Florida wrapping up power restoration following Hurricane Isaias; strategic grid improvements delivered customer benefits</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>天災</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>0.876</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMilwJBVV95cUxQSE56WFAwZGtmSkx6bmxuYlVYRGZORjdyWHh3aXYxakpGY3dIbUxLQTNxZ3FYdnFBWEtiU3F1VlFRMWFtaUs5V19adTlRVklodGNMSmFHOGgxWmFjV0R0R2pOSXVJZEEtNXd1NVFlcGlyMGpUZHJBUHp1T1dFWTA4SElLOGhLc2pfZC1zVm9vN1J6QjJ6YlRiUUJLcG9Ybzk1bFJVQjFHbkw4NHhqak1YcTRFYTJBeElzamU0STVlcGx0Sm5aWnhrREVhWFNpT0lINWdXcEFxRllvWkEyLXQxSm1YNzdvaGEtRGtoZzJsVE52QWpMLUVCSklwc1phUUVTUEJPTXpDaFlHb0tIckppR0FmQjRZSUU?oc=5</t>
         </is>
       </c>
-      <c r="V3" s="3" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>PR Newswire</t>
         </is>
       </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr">
+      <c r="W3" s="2" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="Y3" s="2" t="inlineStr">
         <is>
           <t>NATURAL_DISASTER</t>
         </is>
       </c>
-      <c r="Z3" s="3" t="inlineStr">
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>hurricane</t>
         </is>
       </c>
-      <c r="AA3" s="3" t="inlineStr">
+      <c r="AA3" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>f0f77ba8cc3347d3fb4b041b</t>
         </is>
       </c>
-      <c r="AD3" s="3" t="inlineStr">
+      <c r="AD3" s="2" t="inlineStr">
         <is>
           <t>866abc5336742a43aacc24cc</t>
         </is>
       </c>
-      <c r="AE3" s="3" t="inlineStr">
+      <c r="AE3" s="2" t="inlineStr">
         <is>
           <t>DUK-NATURAL_DISASTER-001</t>
         </is>
       </c>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr"/>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
+      <c r="AF3" s="2" t="inlineStr"/>
+      <c r="AG3" s="2" t="inlineStr"/>
+      <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AK3" s="2" t="inlineStr"/>
+      <c r="AL3" s="2" t="inlineStr"/>
+      <c r="AM3" s="2" t="inlineStr"/>
+      <c r="AN3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AP3" s="2" t="inlineStr"/>
+      <c r="AQ3" s="2" t="inlineStr"/>
+      <c r="AR3" s="2" t="inlineStr"/>
+      <c r="AS3" s="2" t="inlineStr"/>
+      <c r="AT3" s="2" t="inlineStr"/>
+      <c r="AU3" s="2" t="inlineStr"/>
+      <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" s="2" t="inlineStr"/>
+      <c r="AX3" s="2" t="inlineStr"/>
+      <c r="AY3" s="2" t="inlineStr"/>
+      <c r="AZ3" s="2" t="inlineStr"/>
+      <c r="BA3" s="2" t="inlineStr"/>
+      <c r="BB3" s="2" t="inlineStr">
         <is>
           <t>DUK</t>
         </is>
       </c>
-      <c r="BC3" s="3" t="inlineStr">
+      <c r="BC3" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="3" t="inlineStr"/>
-      <c r="BE3" s="3" t="inlineStr">
+      <c r="BD3" s="2" t="inlineStr"/>
+      <c r="BE3" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF3" s="3" t="inlineStr"/>
-      <c r="BG3" s="3" t="inlineStr">
+      <c r="BF3" s="2" t="inlineStr"/>
+      <c r="BG3" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1204,28 +1260,32 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>監管調查</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1265,7 +1325,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>REGULATORY_INVESTIGATION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -1278,7 +1338,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>68c5367c86014e3fa87cd56732332409</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>a8c475715ee1d4253926397c</t>
@@ -1303,7 +1367,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -1339,2745 +1407,2849 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Apple Inc.</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>2026-10-10T19:57:29+08:00</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Apple (AAPL) Could Be 33% Overvalued Following Formula 1 Streaming Buzz</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>估值疑慮</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0.66</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNT0tDV24tNm9jMlREWmNzQUdvT2lxRkl0WEVMQTNKbVZPMHFUTWcxMGszQXI5REpLdkZoblJzd29QdDVQMlFMYzJtUm9LbWgwUjVBZC1GY1plX0RDOVJQRlF2ZkpZZXV5alhHaDdrRjh0QUhsR3RjdGloNTJicGIyQzAzWW80UU5VOUk1ZlV4ZGpraWM0ZzhYZ0dZYnYwdjF1ZURIdmVyQjdEc1NVUm5MeTNXVjJkTVRMVFkyStIBwgFBVV95cUxNNUlnYkNGOWhURWRRSjNNcWxPaFA0UTMxVDFkTnRBUWw0djJzNGZiOUVUTWlWZFFXTE9tWkVzVldQRzhxajZ1NFNyTHZoSWQ0VEQwR2ZHUGFVMVhsam9pX3ZoZkcyY2UzMXhUZHBiSnNSV0dTczdmazhXTzRfZG5lSTNoOUJlcXVRcEV4TjM1QnB2bFdjZ2tmd3pGVHVUSE55eGJvMG0waE9xQTlyRDdMd3pQQVJ0ZGtaZU95bGl6bk9kQQ?oc=5</t>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Simply Wall Street</t>
         </is>
       </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr">
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
+      <c r="Y5" s="2" t="inlineStr">
         <is>
           <t>VALUATION_CONCERN</t>
         </is>
       </c>
-      <c r="Z5" s="3" t="inlineStr">
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>overvalued</t>
         </is>
       </c>
-      <c r="AA5" s="3" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB5" s="3" t="inlineStr"/>
-      <c r="AC5" s="3" t="inlineStr">
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>a03d519accae46b313527dd7</t>
         </is>
       </c>
-      <c r="AD5" s="3" t="inlineStr">
+      <c r="AD5" s="2" t="inlineStr">
         <is>
           <t>562417aa9cb18c87f7cf45e1</t>
         </is>
       </c>
-      <c r="AE5" s="3" t="inlineStr">
+      <c r="AE5" s="2" t="inlineStr">
         <is>
           <t>AAPL-VALUATION_CONCERN-001</t>
         </is>
       </c>
-      <c r="AF5" s="3" t="inlineStr"/>
-      <c r="AG5" s="3" t="inlineStr"/>
-      <c r="AH5" s="3" t="inlineStr"/>
-      <c r="AI5" s="3" t="inlineStr"/>
-      <c r="AJ5" s="3" t="inlineStr"/>
-      <c r="AK5" s="3" t="inlineStr"/>
-      <c r="AL5" s="3" t="inlineStr"/>
-      <c r="AM5" s="3" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
-      <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr">
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AK5" s="2" t="inlineStr"/>
+      <c r="AL5" s="2" t="inlineStr"/>
+      <c r="AM5" s="2" t="inlineStr"/>
+      <c r="AN5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AP5" s="2" t="inlineStr"/>
+      <c r="AQ5" s="2" t="inlineStr"/>
+      <c r="AR5" s="2" t="inlineStr"/>
+      <c r="AS5" s="2" t="inlineStr"/>
+      <c r="AT5" s="2" t="inlineStr"/>
+      <c r="AU5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX5" s="3" t="inlineStr"/>
-      <c r="AY5" s="3" t="inlineStr"/>
-      <c r="AZ5" s="3" t="inlineStr"/>
-      <c r="BA5" s="3" t="inlineStr"/>
-      <c r="BB5" s="3" t="inlineStr">
+      <c r="AX5" s="2" t="inlineStr"/>
+      <c r="AY5" s="2" t="inlineStr"/>
+      <c r="AZ5" s="2" t="inlineStr"/>
+      <c r="BA5" s="2" t="inlineStr"/>
+      <c r="BB5" s="2" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="BC5" s="3" t="inlineStr">
+      <c r="BC5" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="3" t="inlineStr"/>
-      <c r="BE5" s="3" t="inlineStr">
+      <c r="BD5" s="2" t="inlineStr"/>
+      <c r="BE5" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF5" s="3" t="inlineStr">
+      <c r="BF5" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG5" s="3" t="inlineStr">
+      <c r="BG5" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>AOS</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>A.O. Smith Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-10-10T17:40:45+08:00</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>A. O. Smith (AOS) Could Be 3% Overvalued Following Softer Sales And EPS</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>估值疑慮</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>'-0.729</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U6" s="3" t="inlineStr">
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPRW1rNjZiMExxMzVVaFQzcEtuWm1tbTFSd25IUVhGRkR1NURnOXZMeUw1QV9vazlESU9GV0l4U2pndTNPa2o4dW54UkR4LXJ5eXg4NGh2Y245WGVrYmo4OG9MeTFpRlp6Xy1HT3VKZnlYOHdINFloU25SV3RSYjU3Z2VwUVdfVm1EQ19vYlU4VXYtRTh1VVhVckUwZVBZM0U0bG9XcUdrSFZRb2tVcnBSMkRqNjVWNEV0VlNvaFRkS3ZtaTFFVXlMUUx30gHPAUFVX3lxTFBxaGhvWF9QRWZMVEh5aUhkMWEtODZpTEN1RE1LWmNDVDRMUmNrVWk0d2poa2ktd2xOdWJpMDM3TjhscTJ4aTZ2UjNHbHlmc0UtV0d6bm1icDFmcTE3dkE5T2h2WXY2YV9MSl9fY01uZ2RfOFY3TEJ5b2Y1bDYxSFZTN3hnNDZQdEtzcXhudjRndnVpcW1vNVFXVFFMT2dScjZCd0c4NzVQTGJrNU9sVF92RmlfZzhvNE5RYXBXaEdaaG5CMkZpSkZFVFJFR2Jpcw?oc=5</t>
         </is>
       </c>
-      <c r="V6" s="3" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Simply Wall Street</t>
         </is>
       </c>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr">
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
+      <c r="Y6" s="2" t="inlineStr">
         <is>
           <t>VALUATION_CONCERN</t>
         </is>
       </c>
-      <c r="Z6" s="3" t="inlineStr">
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>overvalued</t>
         </is>
       </c>
-      <c r="AA6" s="3" t="inlineStr">
+      <c r="AA6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="3" t="inlineStr">
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>9b74328762308f6419882e27</t>
         </is>
       </c>
-      <c r="AD6" s="3" t="inlineStr">
+      <c r="AD6" s="2" t="inlineStr">
         <is>
           <t>34b9c8984199b3c5b840c158</t>
         </is>
       </c>
-      <c r="AE6" s="3" t="inlineStr">
+      <c r="AE6" s="2" t="inlineStr">
         <is>
           <t>AOS-VALUATION_CONCERN-001</t>
         </is>
       </c>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr">
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" s="2" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" s="2" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr"/>
+      <c r="AP6" s="2" t="inlineStr"/>
+      <c r="AQ6" s="2" t="inlineStr"/>
+      <c r="AR6" s="2" t="inlineStr"/>
+      <c r="AS6" s="2" t="inlineStr"/>
+      <c r="AT6" s="2" t="inlineStr"/>
+      <c r="AU6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
+      <c r="AX6" s="2" t="inlineStr"/>
+      <c r="AY6" s="2" t="inlineStr"/>
+      <c r="AZ6" s="2" t="inlineStr"/>
+      <c r="BA6" s="2" t="inlineStr"/>
+      <c r="BB6" s="2" t="inlineStr">
         <is>
           <t>AOS</t>
         </is>
       </c>
-      <c r="BC6" s="3" t="inlineStr">
+      <c r="BC6" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
+      <c r="BD6" s="2" t="inlineStr"/>
+      <c r="BE6" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="3" t="inlineStr">
+      <c r="BF6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="3" t="inlineStr">
+      <c r="BG6" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr"/>
+      <c r="BL6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>ETN</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Eaton Corporation, PLC Ordinary Shares</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>2026-10-10T16:16:55+08:00</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Eaton (ETN) Stock May Look Overvalued As Cash Flow Lags Its Run</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>估值疑慮</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>'-0.921</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U7" s="3" t="inlineStr">
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNWUJ4Znp4RGtJY1EtT1RnZnB6YjAxYjVodHdZX1pzVzJCQU9aTkRLVXpOTHJmbWhnekdDMDNodW9ZcmY1U0oyWW9GRUlQUVdGck5KWWJ0T2h5R29FMXpFckw2ZU03Y3VJWGYwRG16Qkl4a3diTjZ0RGR0UDFqWHkxV2FwanJ0dTY4RXRDUktVNkNHVUU?oc=5</t>
         </is>
       </c>
-      <c r="V7" s="3" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
+      <c r="Y7" s="2" t="inlineStr">
         <is>
           <t>VALUATION_CONCERN</t>
         </is>
       </c>
-      <c r="Z7" s="3" t="inlineStr">
+      <c r="Z7" s="2" t="inlineStr">
         <is>
           <t>overvalued</t>
         </is>
       </c>
-      <c r="AA7" s="3" t="inlineStr">
+      <c r="AA7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>649824e2d268d058f0ad4c21</t>
         </is>
       </c>
-      <c r="AD7" s="3" t="inlineStr">
+      <c r="AD7" s="2" t="inlineStr">
         <is>
           <t>49a89ed9d6234f8ac82aae3a</t>
         </is>
       </c>
-      <c r="AE7" s="3" t="inlineStr">
+      <c r="AE7" s="2" t="inlineStr">
         <is>
           <t>ETN-VALUATION_CONCERN-001</t>
         </is>
       </c>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr">
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+      <c r="AK7" s="2" t="inlineStr"/>
+      <c r="AL7" s="2" t="inlineStr"/>
+      <c r="AM7" s="2" t="inlineStr"/>
+      <c r="AN7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AP7" s="2" t="inlineStr"/>
+      <c r="AQ7" s="2" t="inlineStr"/>
+      <c r="AR7" s="2" t="inlineStr"/>
+      <c r="AS7" s="2" t="inlineStr"/>
+      <c r="AT7" s="2" t="inlineStr"/>
+      <c r="AU7" s="2" t="inlineStr"/>
+      <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
+      <c r="AX7" s="2" t="inlineStr"/>
+      <c r="AY7" s="2" t="inlineStr"/>
+      <c r="AZ7" s="2" t="inlineStr"/>
+      <c r="BA7" s="2" t="inlineStr"/>
+      <c r="BB7" s="2" t="inlineStr">
         <is>
           <t>ETN</t>
         </is>
       </c>
-      <c r="BC7" s="3" t="inlineStr">
+      <c r="BC7" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
+      <c r="BD7" s="2" t="inlineStr"/>
+      <c r="BE7" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF7" s="3" t="inlineStr">
+      <c r="BF7" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG7" s="3" t="inlineStr">
+      <c r="BG7" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr"/>
+      <c r="BL7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>ABT</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Abbott Laboratories</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>2026-10-10T16:13:54+08:00</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Abbott (ABT) Stock Could Be 24% Overvalued After Heart Failure News</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>估值疑慮</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>'-0.106</t>
         </is>
       </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U8" s="3" t="inlineStr">
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOSUxqb240M2o4VW9mWTlIZ2czWktrOEhVa0REOHlLY1RYMXEzZ0tzd3gtb3dPbVRsUml5a0NyMzc4OWVfZXYzNnpZLVNEUG5HV2I1djNPcHpPenBCLWNvQzJ4TFM2dnNkeWp3TENUVWlPcDVRS3ZZUDQyckVjS2tJUTlqWWxfWDRiLVJhRW9rc2xkcVpa?oc=5</t>
         </is>
       </c>
-      <c r="V8" s="3" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr">
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
+      <c r="Y8" s="2" t="inlineStr">
         <is>
           <t>VALUATION_CONCERN</t>
         </is>
       </c>
-      <c r="Z8" s="3" t="inlineStr">
+      <c r="Z8" s="2" t="inlineStr">
         <is>
           <t>overvalued</t>
         </is>
       </c>
-      <c r="AA8" s="3" t="inlineStr">
+      <c r="AA8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB8" s="3" t="inlineStr"/>
-      <c r="AC8" s="3" t="inlineStr">
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>6d237aea5670dbfdca2da9bf</t>
         </is>
       </c>
-      <c r="AD8" s="3" t="inlineStr">
+      <c r="AD8" s="2" t="inlineStr">
         <is>
           <t>7e3baac4f8b9d47f1f9dacc1</t>
         </is>
       </c>
-      <c r="AE8" s="3" t="inlineStr">
+      <c r="AE8" s="2" t="inlineStr">
         <is>
           <t>ABT-VALUATION_CONCERN-001</t>
         </is>
       </c>
-      <c r="AF8" s="3" t="inlineStr"/>
-      <c r="AG8" s="3" t="inlineStr"/>
-      <c r="AH8" s="3" t="inlineStr"/>
-      <c r="AI8" s="3" t="inlineStr"/>
-      <c r="AJ8" s="3" t="inlineStr"/>
-      <c r="AK8" s="3" t="inlineStr"/>
-      <c r="AL8" s="3" t="inlineStr"/>
-      <c r="AM8" s="3" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr"/>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr">
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AK8" s="2" t="inlineStr"/>
+      <c r="AL8" s="2" t="inlineStr"/>
+      <c r="AM8" s="2" t="inlineStr"/>
+      <c r="AN8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr"/>
+      <c r="AP8" s="2" t="inlineStr"/>
+      <c r="AQ8" s="2" t="inlineStr"/>
+      <c r="AR8" s="2" t="inlineStr"/>
+      <c r="AS8" s="2" t="inlineStr"/>
+      <c r="AT8" s="2" t="inlineStr"/>
+      <c r="AU8" s="2" t="inlineStr"/>
+      <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr">
+      <c r="AX8" s="2" t="inlineStr"/>
+      <c r="AY8" s="2" t="inlineStr"/>
+      <c r="AZ8" s="2" t="inlineStr"/>
+      <c r="BA8" s="2" t="inlineStr"/>
+      <c r="BB8" s="2" t="inlineStr">
         <is>
           <t>ABT</t>
         </is>
       </c>
-      <c r="BC8" s="3" t="inlineStr">
+      <c r="BC8" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="3" t="inlineStr"/>
-      <c r="BE8" s="3" t="inlineStr">
+      <c r="BD8" s="2" t="inlineStr"/>
+      <c r="BE8" s="2" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1800/000162828026028357/R1.htm</t>
         </is>
       </c>
-      <c r="BF8" s="3" t="inlineStr">
+      <c r="BF8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="BG8" s="3" t="inlineStr">
+      <c r="BG8" s="2" t="inlineStr">
         <is>
           <t>上市公司</t>
         </is>
       </c>
-      <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr"/>
+      <c r="BL8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>TMUS</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>T-Mobile US</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>2026-10-10T11:51:07+08:00</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>SpaceX挑戰美國三大運營商 美國運營商巨頭股價暴跌</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>股價下跌</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0.036</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr">
         <is>
           <t>人工覆核優先</t>
         </is>
       </c>
-      <c r="U9" s="3" t="inlineStr">
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>https://www.gelonghui.com/live/2704388</t>
         </is>
       </c>
-      <c r="V9" s="3" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>TradingView</t>
         </is>
       </c>
-      <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr">
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
+      <c r="Y9" s="2" t="inlineStr">
         <is>
           <t>PRICE_MOVEMENT</t>
         </is>
       </c>
-      <c r="Z9" s="3" t="inlineStr">
+      <c r="Z9" s="2" t="inlineStr">
         <is>
           <t>股價暴跌</t>
         </is>
       </c>
-      <c r="AA9" s="3" t="inlineStr">
+      <c r="AA9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB9" s="3" t="inlineStr"/>
-      <c r="AC9" s="3" t="inlineStr">
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>9be7f426b71d4c91b7ba4737</t>
         </is>
       </c>
-      <c r="AD9" s="3" t="inlineStr">
+      <c r="AD9" s="2" t="inlineStr">
         <is>
           <t>57c8e5c18b2c345a45a74c51</t>
         </is>
       </c>
-      <c r="AE9" s="3" t="inlineStr">
+      <c r="AE9" s="2" t="inlineStr">
         <is>
           <t>TMUS-PRICE_MOVEMENT-001</t>
         </is>
       </c>
-      <c r="AF9" s="3" t="inlineStr"/>
-      <c r="AG9" s="3" t="inlineStr"/>
-      <c r="AH9" s="3" t="inlineStr"/>
-      <c r="AI9" s="3" t="inlineStr"/>
-      <c r="AJ9" s="3" t="inlineStr"/>
-      <c r="AK9" s="3" t="inlineStr"/>
-      <c r="AL9" s="3" t="inlineStr"/>
-      <c r="AM9" s="3" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
-      <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="3" t="inlineStr"/>
-      <c r="AT9" s="3" t="inlineStr"/>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr"/>
-      <c r="AX9" s="3" t="inlineStr"/>
-      <c r="AY9" s="3" t="inlineStr"/>
-      <c r="AZ9" s="3" t="inlineStr"/>
-      <c r="BA9" s="3" t="inlineStr"/>
-      <c r="BB9" s="3" t="inlineStr"/>
-      <c r="BC9" s="3" t="inlineStr">
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+      <c r="AK9" s="2" t="inlineStr"/>
+      <c r="AL9" s="2" t="inlineStr"/>
+      <c r="AM9" s="2" t="inlineStr"/>
+      <c r="AN9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr"/>
+      <c r="AP9" s="2" t="inlineStr"/>
+      <c r="AQ9" s="2" t="inlineStr"/>
+      <c r="AR9" s="2" t="inlineStr"/>
+      <c r="AS9" s="2" t="inlineStr"/>
+      <c r="AT9" s="2" t="inlineStr"/>
+      <c r="AU9" s="2" t="inlineStr"/>
+      <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" s="2" t="inlineStr"/>
+      <c r="AX9" s="2" t="inlineStr"/>
+      <c r="AY9" s="2" t="inlineStr"/>
+      <c r="AZ9" s="2" t="inlineStr"/>
+      <c r="BA9" s="2" t="inlineStr"/>
+      <c r="BB9" s="2" t="inlineStr"/>
+      <c r="BC9" s="2" t="inlineStr">
         <is>
           <t>人工確認</t>
         </is>
       </c>
-      <c r="BD9" s="3" t="inlineStr"/>
-      <c r="BE9" s="3" t="inlineStr"/>
-      <c r="BF9" s="3" t="inlineStr"/>
-      <c r="BG9" s="3" t="inlineStr"/>
-      <c r="BH9" s="3" t="inlineStr">
+      <c r="BD9" s="2" t="inlineStr"/>
+      <c r="BE9" s="2" t="inlineStr"/>
+      <c r="BF9" s="2" t="inlineStr"/>
+      <c r="BG9" s="2" t="inlineStr"/>
+      <c r="BH9" s="2" t="inlineStr">
         <is>
           <t>保留人工代號；目前新聞文字無法自動佐證</t>
         </is>
       </c>
+      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr"/>
+      <c r="BL9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>AT&amp;T</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>2026-10-10T11:51:07+08:00</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>SpaceX挑戰美國三大運營商 美國運營商巨頭股價暴跌</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>股價下跌</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0.036</t>
         </is>
       </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>人工覆核優先</t>
         </is>
       </c>
-      <c r="U10" s="3" t="inlineStr">
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>https://www.gelonghui.com/live/2704388</t>
         </is>
       </c>
-      <c r="V10" s="3" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>TradingView</t>
         </is>
       </c>
-      <c r="W10" s="3" t="inlineStr"/>
-      <c r="X10" s="3" t="inlineStr">
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
+      <c r="Y10" s="2" t="inlineStr">
         <is>
           <t>PRICE_MOVEMENT</t>
         </is>
       </c>
-      <c r="Z10" s="3" t="inlineStr">
+      <c r="Z10" s="2" t="inlineStr">
         <is>
           <t>股價暴跌</t>
         </is>
       </c>
-      <c r="AA10" s="3" t="inlineStr">
+      <c r="AA10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB10" s="3" t="inlineStr"/>
-      <c r="AC10" s="3" t="inlineStr">
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>9be7f426b71d4c91b7ba4737</t>
         </is>
       </c>
-      <c r="AD10" s="3" t="inlineStr">
+      <c r="AD10" s="2" t="inlineStr">
         <is>
           <t>f06fea4c38810e54c31c769d</t>
         </is>
       </c>
-      <c r="AE10" s="3" t="inlineStr">
+      <c r="AE10" s="2" t="inlineStr">
         <is>
           <t>T-PRICE_MOVEMENT-001</t>
         </is>
       </c>
-      <c r="AF10" s="3" t="inlineStr"/>
-      <c r="AG10" s="3" t="inlineStr"/>
-      <c r="AH10" s="3" t="inlineStr"/>
-      <c r="AI10" s="3" t="inlineStr"/>
-      <c r="AJ10" s="3" t="inlineStr"/>
-      <c r="AK10" s="3" t="inlineStr"/>
-      <c r="AL10" s="3" t="inlineStr"/>
-      <c r="AM10" s="3" t="inlineStr"/>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
-      <c r="AP10" s="3" t="inlineStr"/>
-      <c r="AQ10" s="3" t="inlineStr"/>
-      <c r="AR10" s="3" t="inlineStr"/>
-      <c r="AS10" s="3" t="inlineStr"/>
-      <c r="AT10" s="3" t="inlineStr"/>
-      <c r="AU10" s="3" t="inlineStr"/>
-      <c r="AV10" s="3" t="inlineStr"/>
-      <c r="AW10" s="3" t="inlineStr"/>
-      <c r="AX10" s="3" t="inlineStr"/>
-      <c r="AY10" s="3" t="inlineStr"/>
-      <c r="AZ10" s="3" t="inlineStr"/>
-      <c r="BA10" s="3" t="inlineStr"/>
-      <c r="BB10" s="3" t="inlineStr"/>
-      <c r="BC10" s="3" t="inlineStr">
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+      <c r="AK10" s="2" t="inlineStr"/>
+      <c r="AL10" s="2" t="inlineStr"/>
+      <c r="AM10" s="2" t="inlineStr"/>
+      <c r="AN10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AP10" s="2" t="inlineStr"/>
+      <c r="AQ10" s="2" t="inlineStr"/>
+      <c r="AR10" s="2" t="inlineStr"/>
+      <c r="AS10" s="2" t="inlineStr"/>
+      <c r="AT10" s="2" t="inlineStr"/>
+      <c r="AU10" s="2" t="inlineStr"/>
+      <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" s="2" t="inlineStr"/>
+      <c r="AX10" s="2" t="inlineStr"/>
+      <c r="AY10" s="2" t="inlineStr"/>
+      <c r="AZ10" s="2" t="inlineStr"/>
+      <c r="BA10" s="2" t="inlineStr"/>
+      <c r="BB10" s="2" t="inlineStr"/>
+      <c r="BC10" s="2" t="inlineStr">
         <is>
           <t>人工確認</t>
         </is>
       </c>
-      <c r="BD10" s="3" t="inlineStr"/>
-      <c r="BE10" s="3" t="inlineStr"/>
-      <c r="BF10" s="3" t="inlineStr"/>
-      <c r="BG10" s="3" t="inlineStr"/>
-      <c r="BH10" s="3" t="inlineStr">
+      <c r="BD10" s="2" t="inlineStr"/>
+      <c r="BE10" s="2" t="inlineStr"/>
+      <c r="BF10" s="2" t="inlineStr"/>
+      <c r="BG10" s="2" t="inlineStr"/>
+      <c r="BH10" s="2" t="inlineStr">
         <is>
           <t>保留人工代號；目前新聞文字無法自動佐證</t>
         </is>
       </c>
+      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr"/>
+      <c r="BL10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>EIX</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Edison International Common Stock</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>2026-10-10T10:26:15+08:00</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Is Edison International (EIX) Undervalued On Rising Wildfire Claims Ahead Of The Deadline?</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>天災</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>'-0.898</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U11" s="3" t="inlineStr">
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQV2dCaThUbF9vbVdYNlU5N2JTUkxaeXJ1bndkU1J3aEN0NVhmYUJycTVaa0xxTHJYVjE0bTlxX1ZBcHE5dzVUTkJVN1o3WTRldXZfQ2tVTGhQcXlNVkExSEpyeUpZdXJHS3BaU0pnUE0weUR5TXRELXBMeHJkWFJkQ082U25MbEkyY3I4eTQ5TTc3U1F5QjJiVkNtcmtxaUpFYlRiNUs4RTViX2doX2ljWG03a0lSQVFlbWJPR25wMFJ5d2dxazRMYjE3YU4xckw4MkJJ0gHYAUFVX3lxTE9yMnVoTGpKLW9mRHFvNkNVN055MDZnRXRQUVpjLXBWRy1LaWx1TExicHNEUmI4ZlpWVVBZM055cTZxYUhUWm5HQXBMeE0zRUViN1pyXzh4NlBSNXQ2ZmlXMkN6T2NseXF0YXVsNmNPb0hxOTR4MVRncjJReHZEUVBzNHpBb3lmdnJOMVVMZjg2NmY1akVOR3hoT25KOW5oUzVJMHcwd3A2UWFZaVZ1VVpxcUMzeXBXOGFvX3RxWHFYcmlzamQtWFRkRGFuWW5LeEowOEFITDJ5Qg?oc=5</t>
         </is>
       </c>
-      <c r="V11" s="3" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Simply Wall Street</t>
         </is>
       </c>
-      <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr">
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
+      <c r="Y11" s="2" t="inlineStr">
         <is>
           <t>NATURAL_DISASTER</t>
         </is>
       </c>
-      <c r="Z11" s="3" t="inlineStr">
+      <c r="Z11" s="2" t="inlineStr">
         <is>
           <t>wildfire</t>
         </is>
       </c>
-      <c r="AA11" s="3" t="inlineStr">
+      <c r="AA11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB11" s="3" t="inlineStr"/>
-      <c r="AC11" s="3" t="inlineStr">
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>fc1a753b967db841d5bdb4ef</t>
         </is>
       </c>
-      <c r="AD11" s="3" t="inlineStr">
+      <c r="AD11" s="2" t="inlineStr">
         <is>
           <t>f3173b1561c005be9ac92982</t>
         </is>
       </c>
-      <c r="AE11" s="3" t="inlineStr">
+      <c r="AE11" s="2" t="inlineStr">
         <is>
           <t>EIX-NATURAL_DISASTER-001</t>
         </is>
       </c>
-      <c r="AF11" s="3" t="inlineStr"/>
-      <c r="AG11" s="3" t="inlineStr"/>
-      <c r="AH11" s="3" t="inlineStr"/>
-      <c r="AI11" s="3" t="inlineStr"/>
-      <c r="AJ11" s="3" t="inlineStr"/>
-      <c r="AK11" s="3" t="inlineStr"/>
-      <c r="AL11" s="3" t="inlineStr"/>
-      <c r="AM11" s="3" t="inlineStr"/>
-      <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr"/>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
-      <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
-      <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="inlineStr">
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+      <c r="AK11" s="2" t="inlineStr"/>
+      <c r="AL11" s="2" t="inlineStr"/>
+      <c r="AM11" s="2" t="inlineStr"/>
+      <c r="AN11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr"/>
+      <c r="AP11" s="2" t="inlineStr"/>
+      <c r="AQ11" s="2" t="inlineStr"/>
+      <c r="AR11" s="2" t="inlineStr"/>
+      <c r="AS11" s="2" t="inlineStr"/>
+      <c r="AT11" s="2" t="inlineStr"/>
+      <c r="AU11" s="2" t="inlineStr"/>
+      <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX11" s="3" t="inlineStr"/>
-      <c r="AY11" s="3" t="inlineStr"/>
-      <c r="AZ11" s="3" t="inlineStr"/>
-      <c r="BA11" s="3" t="inlineStr"/>
-      <c r="BB11" s="3" t="inlineStr">
+      <c r="AX11" s="2" t="inlineStr"/>
+      <c r="AY11" s="2" t="inlineStr"/>
+      <c r="AZ11" s="2" t="inlineStr"/>
+      <c r="BA11" s="2" t="inlineStr"/>
+      <c r="BB11" s="2" t="inlineStr">
         <is>
           <t>EIX</t>
         </is>
       </c>
-      <c r="BC11" s="3" t="inlineStr">
+      <c r="BC11" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD11" s="3" t="inlineStr"/>
-      <c r="BE11" s="3" t="inlineStr">
+      <c r="BD11" s="2" t="inlineStr"/>
+      <c r="BE11" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF11" s="3" t="inlineStr">
+      <c r="BF11" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG11" s="3" t="inlineStr">
+      <c r="BG11" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BH11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BJ11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr"/>
+      <c r="BL11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>PWR</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Quanta Services, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>2026-10-10T10:13:00+08:00</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Is Quanta Services (PWR) Overvalued As AI Demand Lifts Growth Hopes?</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>估值疑慮</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0.833</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U12" s="3" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNek9lNFhsaDdnY1JnMDJLbHFmc0Nzd21USVdqWDJKeExkRlNjMU54ZkplR2lnVXJ3c0xscVFsRXBZWGJuMk5uek1KYWRrRVRXZWFoYmtWeXMyMVhMT1UwaXZ2WlBjdDA2Z1FTQU1oTl9mNGVJNUVQajVVcU1MMjI2eWxpNzF3OXVqNVpYaHA5bjlUS19vZ0hlaTdES1NRQ3c?oc=5</t>
         </is>
       </c>
-      <c r="V12" s="3" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W12" s="3" t="inlineStr"/>
-      <c r="X12" s="3" t="inlineStr">
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
+      <c r="Y12" s="2" t="inlineStr">
         <is>
           <t>VALUATION_CONCERN</t>
         </is>
       </c>
-      <c r="Z12" s="3" t="inlineStr">
+      <c r="Z12" s="2" t="inlineStr">
         <is>
           <t>overvalued</t>
         </is>
       </c>
-      <c r="AA12" s="3" t="inlineStr">
+      <c r="AA12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB12" s="3" t="inlineStr"/>
-      <c r="AC12" s="3" t="inlineStr">
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
         <is>
           <t>0d0608c617221536e2d0e989</t>
         </is>
       </c>
-      <c r="AD12" s="3" t="inlineStr">
+      <c r="AD12" s="2" t="inlineStr">
         <is>
           <t>1115b03dd6f059ce26b684cc</t>
         </is>
       </c>
-      <c r="AE12" s="3" t="inlineStr">
+      <c r="AE12" s="2" t="inlineStr">
         <is>
           <t>PWR-VALUATION_CONCERN-001</t>
         </is>
       </c>
-      <c r="AF12" s="3" t="inlineStr"/>
-      <c r="AG12" s="3" t="inlineStr"/>
-      <c r="AH12" s="3" t="inlineStr"/>
-      <c r="AI12" s="3" t="inlineStr"/>
-      <c r="AJ12" s="3" t="inlineStr"/>
-      <c r="AK12" s="3" t="inlineStr"/>
-      <c r="AL12" s="3" t="inlineStr"/>
-      <c r="AM12" s="3" t="inlineStr"/>
-      <c r="AN12" s="3" t="inlineStr"/>
-      <c r="AO12" s="3" t="inlineStr"/>
-      <c r="AP12" s="3" t="inlineStr"/>
-      <c r="AQ12" s="3" t="inlineStr"/>
-      <c r="AR12" s="3" t="inlineStr"/>
-      <c r="AS12" s="3" t="inlineStr"/>
-      <c r="AT12" s="3" t="inlineStr"/>
-      <c r="AU12" s="3" t="inlineStr"/>
-      <c r="AV12" s="3" t="inlineStr"/>
-      <c r="AW12" s="3" t="inlineStr">
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+      <c r="AK12" s="2" t="inlineStr"/>
+      <c r="AL12" s="2" t="inlineStr"/>
+      <c r="AM12" s="2" t="inlineStr"/>
+      <c r="AN12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr"/>
+      <c r="AP12" s="2" t="inlineStr"/>
+      <c r="AQ12" s="2" t="inlineStr"/>
+      <c r="AR12" s="2" t="inlineStr"/>
+      <c r="AS12" s="2" t="inlineStr"/>
+      <c r="AT12" s="2" t="inlineStr"/>
+      <c r="AU12" s="2" t="inlineStr"/>
+      <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX12" s="3" t="inlineStr"/>
-      <c r="AY12" s="3" t="inlineStr"/>
-      <c r="AZ12" s="3" t="inlineStr"/>
-      <c r="BA12" s="3" t="inlineStr"/>
-      <c r="BB12" s="3" t="inlineStr">
+      <c r="AX12" s="2" t="inlineStr"/>
+      <c r="AY12" s="2" t="inlineStr"/>
+      <c r="AZ12" s="2" t="inlineStr"/>
+      <c r="BA12" s="2" t="inlineStr"/>
+      <c r="BB12" s="2" t="inlineStr">
         <is>
           <t>PWR</t>
         </is>
       </c>
-      <c r="BC12" s="3" t="inlineStr">
+      <c r="BC12" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD12" s="3" t="inlineStr"/>
-      <c r="BE12" s="3" t="inlineStr">
+      <c r="BD12" s="2" t="inlineStr"/>
+      <c r="BE12" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF12" s="3" t="inlineStr">
+      <c r="BF12" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG12" s="3" t="inlineStr">
+      <c r="BG12" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH12" s="3" t="inlineStr"/>
+      <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr"/>
+      <c r="BL12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>EXPD</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Expeditors International</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>2026-10-10T09:50:00+08:00</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Expeditors International Of Washington (EXPD) Could Be 9% Overvalued As Compliance Calls Draw Focus</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>估值疑慮</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>'-0.265</t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr"/>
-      <c r="S13" s="3" t="inlineStr"/>
-      <c r="T13" s="3" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U13" s="3" t="inlineStr">
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQa1lMbGo0WG1sbjRpUXBIYVRrTHp5Qmt1YzNSUC1IUUhvNGU0U0JneElnb0tzRVZHMjFuZnJya3NrdnpxMlQtSjBUQjJNQTY5MXBHTWwwYV80V0ZNLU9MTkVmLVREY0ZBRXU4SE14cDJvT2lWN05QenVwS0tWYjlqMlhGMktDWFg3dnhTZjd6ZjlaVDByQjc3d3NoUWlvLThVOElkLXdyRlBJb3lReUs3Sjl1Tmx3M2dqTnh3WVFKWkRSRTlxblpSYm95Skc5ZW5nYUhSNnBqQVFzTnB4ZFI5MnEtUlk0OHF3bHh6RzdtdVpsSjDSAfgBQVVfeXFMTkV6T3l3V3Fvc2haRVUtdVhOaWl6TmJRT0JNRDJObnNDVGpoX2NfU2dPZTRndzNPa3RRN05sZDJ0WldCeVhoUlpZQ2F6ZHFLeUVlX1VhaEtVaklMU1lVUURMYWpfaG9DeXNxWmh3S0Yxd0hIS1pSQ3JmYnRLZXBFNjk1ajZZeTYxRHhjaVFsblhEN1JsU2JHWWt6QkVYaEo5TzJfWGdiWTJ1XzVYcy1PMEhpT1E4QWNiMW9SSzVqQUNDdWdqS3FUOHRuck83QjJWWVRsQjdISHBvMkFFUlpMdTFzNk1USk9MS2dLUFV1MW5lelIxOHlrOGw?oc=5</t>
         </is>
       </c>
-      <c r="V13" s="3" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Simply Wall Street</t>
         </is>
       </c>
-      <c r="W13" s="3" t="inlineStr"/>
-      <c r="X13" s="3" t="inlineStr">
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
+      <c r="Y13" s="2" t="inlineStr">
         <is>
           <t>VALUATION_CONCERN</t>
         </is>
       </c>
-      <c r="Z13" s="3" t="inlineStr">
+      <c r="Z13" s="2" t="inlineStr">
         <is>
           <t>overvalued</t>
         </is>
       </c>
-      <c r="AA13" s="3" t="inlineStr">
+      <c r="AA13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB13" s="3" t="inlineStr"/>
-      <c r="AC13" s="3" t="inlineStr">
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
         <is>
           <t>0fc35c0667c313f8102e2fee</t>
         </is>
       </c>
-      <c r="AD13" s="3" t="inlineStr">
+      <c r="AD13" s="2" t="inlineStr">
         <is>
           <t>f5ce51c4c674fdc8226b62cb</t>
         </is>
       </c>
-      <c r="AE13" s="3" t="inlineStr">
+      <c r="AE13" s="2" t="inlineStr">
         <is>
           <t>EXPD-VALUATION_CONCERN-001</t>
         </is>
       </c>
-      <c r="AF13" s="3" t="inlineStr"/>
-      <c r="AG13" s="3" t="inlineStr"/>
-      <c r="AH13" s="3" t="inlineStr"/>
-      <c r="AI13" s="3" t="inlineStr"/>
-      <c r="AJ13" s="3" t="inlineStr"/>
-      <c r="AK13" s="3" t="inlineStr"/>
-      <c r="AL13" s="3" t="inlineStr"/>
-      <c r="AM13" s="3" t="inlineStr"/>
-      <c r="AN13" s="3" t="inlineStr"/>
-      <c r="AO13" s="3" t="inlineStr"/>
-      <c r="AP13" s="3" t="inlineStr"/>
-      <c r="AQ13" s="3" t="inlineStr"/>
-      <c r="AR13" s="3" t="inlineStr"/>
-      <c r="AS13" s="3" t="inlineStr"/>
-      <c r="AT13" s="3" t="inlineStr"/>
-      <c r="AU13" s="3" t="inlineStr"/>
-      <c r="AV13" s="3" t="inlineStr"/>
-      <c r="AW13" s="3" t="inlineStr"/>
-      <c r="AX13" s="3" t="inlineStr"/>
-      <c r="AY13" s="3" t="inlineStr"/>
-      <c r="AZ13" s="3" t="inlineStr"/>
-      <c r="BA13" s="3" t="inlineStr"/>
-      <c r="BB13" s="3" t="inlineStr">
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+      <c r="AK13" s="2" t="inlineStr"/>
+      <c r="AL13" s="2" t="inlineStr"/>
+      <c r="AM13" s="2" t="inlineStr"/>
+      <c r="AN13" s="2" t="inlineStr"/>
+      <c r="AO13" s="2" t="inlineStr"/>
+      <c r="AP13" s="2" t="inlineStr"/>
+      <c r="AQ13" s="2" t="inlineStr"/>
+      <c r="AR13" s="2" t="inlineStr"/>
+      <c r="AS13" s="2" t="inlineStr"/>
+      <c r="AT13" s="2" t="inlineStr"/>
+      <c r="AU13" s="2" t="inlineStr"/>
+      <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" s="2" t="inlineStr"/>
+      <c r="AX13" s="2" t="inlineStr"/>
+      <c r="AY13" s="2" t="inlineStr"/>
+      <c r="AZ13" s="2" t="inlineStr"/>
+      <c r="BA13" s="2" t="inlineStr"/>
+      <c r="BB13" s="2" t="inlineStr">
         <is>
           <t>EXPD</t>
         </is>
       </c>
-      <c r="BC13" s="3" t="inlineStr">
+      <c r="BC13" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD13" s="3" t="inlineStr"/>
-      <c r="BE13" s="3" t="inlineStr">
+      <c r="BD13" s="2" t="inlineStr"/>
+      <c r="BE13" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF13" s="3" t="inlineStr"/>
-      <c r="BG13" s="3" t="inlineStr">
+      <c r="BF13" s="2" t="inlineStr"/>
+      <c r="BG13" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH13" s="3" t="inlineStr"/>
+      <c r="BH13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr"/>
+      <c r="BJ13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr"/>
+      <c r="BL13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>CMCSA</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Comcast Corporation</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>2026-10-10T06:10:55+08:00</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Comcast Opens More Than 26,000 Public Xfinity WiFi Hotspots Across Florida’s Panhandle, Alabama, Mississippi and Louisiana Ahead of Hurricane Isaias</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>天災</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0.235</t>
         </is>
       </c>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
-      <c r="T14" s="3" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U14" s="3" t="inlineStr">
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOOW9pTW9fS0ZOQ3EzNEEtNHE5aXhtYU1qRU5ma05jR09pbkVaa2d1S2pDb1pDUHc5Nnc3X0szWVp2XzBiMExhUTU0S3pjS3RNWFR3ekRlQTlwYkx5enIzb1VKSDBpellsLWY0LW1QOFNZbURPa3NGQmdYYVMyV01DR1JWNjJGaTJQYWs2a1RwRmxiSDFjQ2stN21RXzJ1Q1pGQmxaWUFxRndTXzhQTkR4RGU3VHROQTdJenR1MHpIcUhNRXhEdUdwNElsUlhOVHNx?oc=5</t>
         </is>
       </c>
-      <c r="V14" s="3" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Comcast Corporation</t>
         </is>
       </c>
-      <c r="W14" s="3" t="inlineStr"/>
-      <c r="X14" s="3" t="inlineStr">
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
+      <c r="Y14" s="2" t="inlineStr">
         <is>
           <t>NATURAL_DISASTER</t>
         </is>
       </c>
-      <c r="Z14" s="3" t="inlineStr">
+      <c r="Z14" s="2" t="inlineStr">
         <is>
           <t>hurricane</t>
         </is>
       </c>
-      <c r="AA14" s="3" t="inlineStr">
+      <c r="AA14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB14" s="3" t="inlineStr"/>
-      <c r="AC14" s="3" t="inlineStr">
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
         <is>
           <t>772cf080a9a1a672a6d4f5f6</t>
         </is>
       </c>
-      <c r="AD14" s="3" t="inlineStr">
+      <c r="AD14" s="2" t="inlineStr">
         <is>
           <t>30c0df88df1e80b9a0c35c11</t>
         </is>
       </c>
-      <c r="AE14" s="3" t="inlineStr">
+      <c r="AE14" s="2" t="inlineStr">
         <is>
           <t>CMCSA-NATURAL_DISASTER-001</t>
         </is>
       </c>
-      <c r="AF14" s="3" t="inlineStr"/>
-      <c r="AG14" s="3" t="inlineStr"/>
-      <c r="AH14" s="3" t="inlineStr"/>
-      <c r="AI14" s="3" t="inlineStr"/>
-      <c r="AJ14" s="3" t="inlineStr"/>
-      <c r="AK14" s="3" t="inlineStr"/>
-      <c r="AL14" s="3" t="inlineStr"/>
-      <c r="AM14" s="3" t="inlineStr"/>
-      <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr"/>
-      <c r="AP14" s="3" t="inlineStr"/>
-      <c r="AQ14" s="3" t="inlineStr"/>
-      <c r="AR14" s="3" t="inlineStr"/>
-      <c r="AS14" s="3" t="inlineStr"/>
-      <c r="AT14" s="3" t="inlineStr"/>
-      <c r="AU14" s="3" t="inlineStr"/>
-      <c r="AV14" s="3" t="inlineStr"/>
-      <c r="AW14" s="3" t="inlineStr">
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+      <c r="AK14" s="2" t="inlineStr"/>
+      <c r="AL14" s="2" t="inlineStr"/>
+      <c r="AM14" s="2" t="inlineStr"/>
+      <c r="AN14" s="2" t="inlineStr"/>
+      <c r="AO14" s="2" t="inlineStr"/>
+      <c r="AP14" s="2" t="inlineStr"/>
+      <c r="AQ14" s="2" t="inlineStr"/>
+      <c r="AR14" s="2" t="inlineStr"/>
+      <c r="AS14" s="2" t="inlineStr"/>
+      <c r="AT14" s="2" t="inlineStr"/>
+      <c r="AU14" s="2" t="inlineStr"/>
+      <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX14" s="3" t="inlineStr"/>
-      <c r="AY14" s="3" t="inlineStr"/>
-      <c r="AZ14" s="3" t="inlineStr"/>
-      <c r="BA14" s="3" t="inlineStr"/>
-      <c r="BB14" s="3" t="inlineStr">
+      <c r="AX14" s="2" t="inlineStr"/>
+      <c r="AY14" s="2" t="inlineStr"/>
+      <c r="AZ14" s="2" t="inlineStr"/>
+      <c r="BA14" s="2" t="inlineStr"/>
+      <c r="BB14" s="2" t="inlineStr">
         <is>
           <t>CMCSA</t>
         </is>
       </c>
-      <c r="BC14" s="3" t="inlineStr">
+      <c r="BC14" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD14" s="3" t="inlineStr"/>
-      <c r="BE14" s="3" t="inlineStr">
+      <c r="BD14" s="2" t="inlineStr"/>
+      <c r="BE14" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF14" s="3" t="inlineStr">
+      <c r="BF14" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG14" s="3" t="inlineStr">
+      <c r="BG14" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH14" s="3" t="inlineStr"/>
+      <c r="BH14" s="2" t="inlineStr"/>
+      <c r="BI14" s="2" t="inlineStr"/>
+      <c r="BJ14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr"/>
+      <c r="BL14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>AT&amp;T</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>2026-10-10T05:07:00+08:00</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>As AT&amp;T, Verizon and T-Mobile shares fall, Wall Street assesses the growing SpaceX threat</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>股價下跌</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>'-0.908</t>
         </is>
       </c>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
-      <c r="T15" s="3" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr">
         <is>
           <t>人工覆核優先</t>
         </is>
       </c>
-      <c r="U15" s="3" t="inlineStr">
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOeWhaS1NCZlJ4VnJsY1d5OFFTNnFPblRlQVBoTFdNeUg0M0JBTUNidVVXWlNMck41Tlc3eXotZjQ1eHBjMWtCbVh2WFFUTC04UHZIOFBpcHU3QUNMY2RxUHJydVQ0WEgwek5rSGU5cjFUcUlVOWE0WUNwOHNQOEVFMk0yZGRzeUsxM3ZRQ25TUENqcmtaVnZpOXV6Nkl2dy11c2JBMFdNamdoNUlyYjQzcnk5YnpWRDd2S1BaQ3JKS0xheGxVejhEUlZ3?oc=5</t>
         </is>
       </c>
-      <c r="V15" s="3" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>MarketWatch</t>
         </is>
       </c>
-      <c r="W15" s="3" t="inlineStr"/>
-      <c r="X15" s="3" t="inlineStr">
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
+      <c r="Y15" s="2" t="inlineStr">
         <is>
           <t>PRICE_MOVEMENT</t>
         </is>
       </c>
-      <c r="Z15" s="3" t="inlineStr">
+      <c r="Z15" s="2" t="inlineStr">
         <is>
           <t>shares fall</t>
         </is>
       </c>
-      <c r="AA15" s="3" t="inlineStr">
+      <c r="AA15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB15" s="3" t="inlineStr"/>
-      <c r="AC15" s="3" t="inlineStr">
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
         <is>
           <t>2d8847c76339218fad2c6db6</t>
         </is>
       </c>
-      <c r="AD15" s="3" t="inlineStr">
+      <c r="AD15" s="2" t="inlineStr">
         <is>
           <t>30c6d5602c48c8a8e5daa9d9</t>
         </is>
       </c>
-      <c r="AE15" s="3" t="inlineStr">
+      <c r="AE15" s="2" t="inlineStr">
         <is>
           <t>T-PRICE_MOVEMENT-001</t>
         </is>
       </c>
-      <c r="AF15" s="3" t="inlineStr"/>
-      <c r="AG15" s="3" t="inlineStr"/>
-      <c r="AH15" s="3" t="inlineStr"/>
-      <c r="AI15" s="3" t="inlineStr"/>
-      <c r="AJ15" s="3" t="inlineStr"/>
-      <c r="AK15" s="3" t="inlineStr"/>
-      <c r="AL15" s="3" t="inlineStr"/>
-      <c r="AM15" s="3" t="inlineStr"/>
-      <c r="AN15" s="3" t="inlineStr"/>
-      <c r="AO15" s="3" t="inlineStr"/>
-      <c r="AP15" s="3" t="inlineStr"/>
-      <c r="AQ15" s="3" t="inlineStr"/>
-      <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr"/>
-      <c r="AT15" s="3" t="inlineStr"/>
-      <c r="AU15" s="3" t="inlineStr"/>
-      <c r="AV15" s="3" t="inlineStr"/>
-      <c r="AW15" s="3" t="inlineStr"/>
-      <c r="AX15" s="3" t="inlineStr"/>
-      <c r="AY15" s="3" t="inlineStr"/>
-      <c r="AZ15" s="3" t="inlineStr"/>
-      <c r="BA15" s="3" t="inlineStr"/>
-      <c r="BB15" s="3" t="inlineStr"/>
-      <c r="BC15" s="3" t="inlineStr">
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+      <c r="AK15" s="2" t="inlineStr"/>
+      <c r="AL15" s="2" t="inlineStr"/>
+      <c r="AM15" s="2" t="inlineStr"/>
+      <c r="AN15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr"/>
+      <c r="AP15" s="2" t="inlineStr"/>
+      <c r="AQ15" s="2" t="inlineStr"/>
+      <c r="AR15" s="2" t="inlineStr"/>
+      <c r="AS15" s="2" t="inlineStr"/>
+      <c r="AT15" s="2" t="inlineStr"/>
+      <c r="AU15" s="2" t="inlineStr"/>
+      <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" s="2" t="inlineStr"/>
+      <c r="AX15" s="2" t="inlineStr"/>
+      <c r="AY15" s="2" t="inlineStr"/>
+      <c r="AZ15" s="2" t="inlineStr"/>
+      <c r="BA15" s="2" t="inlineStr"/>
+      <c r="BB15" s="2" t="inlineStr"/>
+      <c r="BC15" s="2" t="inlineStr">
         <is>
           <t>人工確認</t>
         </is>
       </c>
-      <c r="BD15" s="3" t="inlineStr"/>
-      <c r="BE15" s="3" t="inlineStr"/>
-      <c r="BF15" s="3" t="inlineStr"/>
-      <c r="BG15" s="3" t="inlineStr"/>
-      <c r="BH15" s="3" t="inlineStr"/>
+      <c r="BD15" s="2" t="inlineStr"/>
+      <c r="BE15" s="2" t="inlineStr"/>
+      <c r="BF15" s="2" t="inlineStr"/>
+      <c r="BG15" s="2" t="inlineStr"/>
+      <c r="BH15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr"/>
+      <c r="BJ15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr"/>
+      <c r="BL15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>VZ</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Verizon</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>2026-10-10T05:07:00+08:00</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>As AT&amp;T, Verizon and T-Mobile shares fall, Wall Street assesses the growing SpaceX threat</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>股價下跌</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>'-0.908</t>
         </is>
       </c>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
-      <c r="T16" s="3" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
         <is>
           <t>人工覆核優先</t>
         </is>
       </c>
-      <c r="U16" s="3" t="inlineStr">
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOeWhaS1NCZlJ4VnJsY1d5OFFTNnFPblRlQVBoTFdNeUg0M0JBTUNidVVXWlNMck41Tlc3eXotZjQ1eHBjMWtCbVh2WFFUTC04UHZIOFBpcHU3QUNMY2RxUHJydVQ0WEgwek5rSGU5cjFUcUlVOWE0WUNwOHNQOEVFMk0yZGRzeUsxM3ZRQ25TUENqcmtaVnZpOXV6Nkl2dy11c2JBMFdNamdoNUlyYjQzcnk5YnpWRDd2S1BaQ3JKS0xheGxVejhEUlZ3?oc=5</t>
         </is>
       </c>
-      <c r="V16" s="3" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>MarketWatch</t>
         </is>
       </c>
-      <c r="W16" s="3" t="inlineStr"/>
-      <c r="X16" s="3" t="inlineStr">
+      <c r="W16" s="2" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
+      <c r="Y16" s="2" t="inlineStr">
         <is>
           <t>PRICE_MOVEMENT</t>
         </is>
       </c>
-      <c r="Z16" s="3" t="inlineStr">
+      <c r="Z16" s="2" t="inlineStr">
         <is>
           <t>shares fall</t>
         </is>
       </c>
-      <c r="AA16" s="3" t="inlineStr">
+      <c r="AA16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB16" s="3" t="inlineStr"/>
-      <c r="AC16" s="3" t="inlineStr">
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
         <is>
           <t>2d8847c76339218fad2c6db6</t>
         </is>
       </c>
-      <c r="AD16" s="3" t="inlineStr">
+      <c r="AD16" s="2" t="inlineStr">
         <is>
           <t>e90ce4eaa1e16eddf83751f2</t>
         </is>
       </c>
-      <c r="AE16" s="3" t="inlineStr">
+      <c r="AE16" s="2" t="inlineStr">
         <is>
           <t>VZ-PRICE_MOVEMENT-001</t>
         </is>
       </c>
-      <c r="AF16" s="3" t="inlineStr"/>
-      <c r="AG16" s="3" t="inlineStr"/>
-      <c r="AH16" s="3" t="inlineStr"/>
-      <c r="AI16" s="3" t="inlineStr"/>
-      <c r="AJ16" s="3" t="inlineStr"/>
-      <c r="AK16" s="3" t="inlineStr"/>
-      <c r="AL16" s="3" t="inlineStr"/>
-      <c r="AM16" s="3" t="inlineStr"/>
-      <c r="AN16" s="3" t="inlineStr"/>
-      <c r="AO16" s="3" t="inlineStr"/>
-      <c r="AP16" s="3" t="inlineStr"/>
-      <c r="AQ16" s="3" t="inlineStr"/>
-      <c r="AR16" s="3" t="inlineStr"/>
-      <c r="AS16" s="3" t="inlineStr"/>
-      <c r="AT16" s="3" t="inlineStr"/>
-      <c r="AU16" s="3" t="inlineStr"/>
-      <c r="AV16" s="3" t="inlineStr"/>
-      <c r="AW16" s="3" t="inlineStr"/>
-      <c r="AX16" s="3" t="inlineStr"/>
-      <c r="AY16" s="3" t="inlineStr"/>
-      <c r="AZ16" s="3" t="inlineStr"/>
-      <c r="BA16" s="3" t="inlineStr"/>
-      <c r="BB16" s="3" t="inlineStr"/>
-      <c r="BC16" s="3" t="inlineStr">
+      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr"/>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr"/>
+      <c r="AK16" s="2" t="inlineStr"/>
+      <c r="AL16" s="2" t="inlineStr"/>
+      <c r="AM16" s="2" t="inlineStr"/>
+      <c r="AN16" s="2" t="inlineStr"/>
+      <c r="AO16" s="2" t="inlineStr"/>
+      <c r="AP16" s="2" t="inlineStr"/>
+      <c r="AQ16" s="2" t="inlineStr"/>
+      <c r="AR16" s="2" t="inlineStr"/>
+      <c r="AS16" s="2" t="inlineStr"/>
+      <c r="AT16" s="2" t="inlineStr"/>
+      <c r="AU16" s="2" t="inlineStr"/>
+      <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" s="2" t="inlineStr"/>
+      <c r="AX16" s="2" t="inlineStr"/>
+      <c r="AY16" s="2" t="inlineStr"/>
+      <c r="AZ16" s="2" t="inlineStr"/>
+      <c r="BA16" s="2" t="inlineStr"/>
+      <c r="BB16" s="2" t="inlineStr"/>
+      <c r="BC16" s="2" t="inlineStr">
         <is>
           <t>人工確認</t>
         </is>
       </c>
-      <c r="BD16" s="3" t="inlineStr"/>
-      <c r="BE16" s="3" t="inlineStr"/>
-      <c r="BF16" s="3" t="inlineStr"/>
-      <c r="BG16" s="3" t="inlineStr"/>
-      <c r="BH16" s="3" t="inlineStr"/>
+      <c r="BD16" s="2" t="inlineStr"/>
+      <c r="BE16" s="2" t="inlineStr"/>
+      <c r="BF16" s="2" t="inlineStr"/>
+      <c r="BG16" s="2" t="inlineStr"/>
+      <c r="BH16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr"/>
+      <c r="BJ16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr"/>
+      <c r="BL16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Uber</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>2026-10-10T03:03:28+08:00</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Deal Dispatch: Uber Buys ezCater For $2.3B, Skydance Takes Over Warner Bros., True Food Kitchen Bankruptcy</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>一般公司更新</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>排除、不納入風險事件</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0.057</t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="3" t="inlineStr"/>
-      <c r="R17" s="3" t="inlineStr"/>
-      <c r="S17" s="3" t="inlineStr"/>
-      <c r="T17" s="3" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr">
         <is>
           <t>人工覆核優先</t>
         </is>
       </c>
-      <c r="U17" s="3" t="inlineStr">
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQMW1EakJNTVNPUnFQcmNHNEFwRWVsX3l0OWU4dmx5M0h5emJOTkp4TzRjekJYVFMzdGtwbWp2SVNqTjh0VjVTcFNPdXltMlNjdVQtVUN3eFZJN2NraFVNUXFZTHlTeVdwcGxDZTZHSDZ5Z3JLMDBleV83ejNSY05NSThGWnIyQmtkUW5FaXZ1YXNkZTRPT2hiVXVNLVZWeHpId3h3UUZGTUQzQlRkazh5TWtsSHdKYXhtTzZpMlpBczItSEpQUGhGaTRDZEJLNDBTZzZKQXZBV19hcXZ4a1E?oc=5</t>
         </is>
       </c>
-      <c r="V17" s="3" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Benzinga</t>
         </is>
       </c>
-      <c r="W17" s="3" t="inlineStr"/>
-      <c r="X17" s="3" t="inlineStr">
+      <c r="W17" s="2" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr">
         <is>
           <t>FINANCIAL</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
+      <c r="Y17" s="2" t="inlineStr">
         <is>
           <t>BANKRUPTCY</t>
         </is>
       </c>
-      <c r="Z17" s="3" t="inlineStr">
+      <c r="Z17" s="2" t="inlineStr">
         <is>
           <t>bankruptcy</t>
         </is>
       </c>
-      <c r="AA17" s="3" t="inlineStr">
+      <c r="AA17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB17" s="3" t="inlineStr"/>
-      <c r="AC17" s="3" t="inlineStr">
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
         <is>
           <t>4654f2f090918d96da79b5df</t>
         </is>
       </c>
-      <c r="AD17" s="3" t="inlineStr">
+      <c r="AD17" s="2" t="inlineStr">
         <is>
           <t>0cfaa1f223a91427c6a34408</t>
         </is>
       </c>
-      <c r="AE17" s="3" t="inlineStr">
+      <c r="AE17" s="2" t="inlineStr">
         <is>
           <t>UBER-BANKRUPTCY-001</t>
         </is>
       </c>
-      <c r="AF17" s="3" t="inlineStr"/>
-      <c r="AG17" s="3" t="inlineStr"/>
-      <c r="AH17" s="3" t="inlineStr"/>
-      <c r="AI17" s="3" t="inlineStr"/>
-      <c r="AJ17" s="3" t="inlineStr"/>
-      <c r="AK17" s="3" t="inlineStr"/>
-      <c r="AL17" s="3" t="inlineStr"/>
-      <c r="AM17" s="3" t="inlineStr"/>
-      <c r="AN17" s="3" t="inlineStr"/>
-      <c r="AO17" s="3" t="inlineStr"/>
-      <c r="AP17" s="3" t="inlineStr"/>
-      <c r="AQ17" s="3" t="inlineStr"/>
-      <c r="AR17" s="3" t="inlineStr"/>
-      <c r="AS17" s="3" t="inlineStr"/>
-      <c r="AT17" s="3" t="inlineStr"/>
-      <c r="AU17" s="3" t="inlineStr"/>
-      <c r="AV17" s="3" t="inlineStr"/>
-      <c r="AW17" s="3" t="inlineStr"/>
-      <c r="AX17" s="3" t="inlineStr"/>
-      <c r="AY17" s="3" t="inlineStr"/>
-      <c r="AZ17" s="3" t="inlineStr"/>
-      <c r="BA17" s="3" t="inlineStr"/>
-      <c r="BB17" s="3" t="inlineStr"/>
-      <c r="BC17" s="3" t="inlineStr">
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr"/>
+      <c r="AI17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr"/>
+      <c r="AK17" s="2" t="inlineStr"/>
+      <c r="AL17" s="2" t="inlineStr"/>
+      <c r="AM17" s="2" t="inlineStr"/>
+      <c r="AN17" s="2" t="inlineStr"/>
+      <c r="AO17" s="2" t="inlineStr"/>
+      <c r="AP17" s="2" t="inlineStr"/>
+      <c r="AQ17" s="2" t="inlineStr"/>
+      <c r="AR17" s="2" t="inlineStr"/>
+      <c r="AS17" s="2" t="inlineStr"/>
+      <c r="AT17" s="2" t="inlineStr"/>
+      <c r="AU17" s="2" t="inlineStr"/>
+      <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" s="2" t="inlineStr"/>
+      <c r="AX17" s="2" t="inlineStr"/>
+      <c r="AY17" s="2" t="inlineStr"/>
+      <c r="AZ17" s="2" t="inlineStr"/>
+      <c r="BA17" s="2" t="inlineStr"/>
+      <c r="BB17" s="2" t="inlineStr"/>
+      <c r="BC17" s="2" t="inlineStr">
         <is>
           <t>人工確認</t>
         </is>
       </c>
-      <c r="BD17" s="3" t="inlineStr"/>
-      <c r="BE17" s="3" t="inlineStr"/>
-      <c r="BF17" s="3" t="inlineStr"/>
-      <c r="BG17" s="3" t="inlineStr"/>
-      <c r="BH17" s="3" t="inlineStr"/>
+      <c r="BD17" s="2" t="inlineStr"/>
+      <c r="BE17" s="2" t="inlineStr"/>
+      <c r="BF17" s="2" t="inlineStr"/>
+      <c r="BG17" s="2" t="inlineStr"/>
+      <c r="BH17" s="2" t="inlineStr"/>
+      <c r="BI17" s="2" t="inlineStr"/>
+      <c r="BJ17" s="2" t="inlineStr"/>
+      <c r="BK17" s="2" t="inlineStr"/>
+      <c r="BL17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Uber Technologies, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>2026-10-10T01:18:00+08:00</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Uber offers free round-trip rides to Florida shelters ahead of Hurricane Isaias</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>天災</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0.167</t>
         </is>
       </c>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
-      <c r="R18" s="3" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr"/>
-      <c r="T18" s="3" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U18" s="3" t="inlineStr">
+      <c r="U18" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOdWpzWnBvdkhRMmd0WWl5WlhCZzdBWXE1dkVtUXZtbWxQSVJRbzg4T0Q3TUtCQjlwZzZTNWZrRFRjVElJNXVic21ibnZ5TDBLTExydXcyb3Q1d25sWGRxMFNTaDBvT19UVTJkajJoSlQwbGc4VUpneVVCd2xPdlRjel9aOVVwT0MweTYxUWNTUHlLN00wUzNDV1NSSl8tRW9FaTJVaW12dVPSAbwBQVVfeXFMUFkzaHNKMl8zSG9HN0NiV200R1U4blhpUzhVSXlLQUVVczdyYXlneWxCN1AycmJ2UXhIckdjTzJONENmUW1FOUg1U3lndFdQRUhId2xPZG85Slg2bC12aVUyQjQtVnFfWmN0b2lfcnQwVHgtMkFXekRaSmljUGFMM2owRE1lSjNETXlGZDl0RGd5ak8zMkh4djVRV0NmYzdIeVJ3ampoQ2NQcVNfbkt5bDQ2cmtjM3JtempOcmI?oc=5</t>
         </is>
       </c>
-      <c r="V18" s="3" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>WCTV</t>
         </is>
       </c>
-      <c r="W18" s="3" t="inlineStr"/>
-      <c r="X18" s="3" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>NATURAL_DISASTER</t>
         </is>
       </c>
-      <c r="Z18" s="3" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>hurricane</t>
         </is>
       </c>
-      <c r="AA18" s="3" t="inlineStr">
+      <c r="AA18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB18" s="3" t="inlineStr"/>
-      <c r="AC18" s="3" t="inlineStr">
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>3221cb812084a113528df1ad</t>
         </is>
       </c>
-      <c r="AD18" s="3" t="inlineStr">
+      <c r="AD18" s="2" t="inlineStr">
         <is>
           <t>e595cb1802c1f232cd047633</t>
         </is>
       </c>
-      <c r="AE18" s="3" t="inlineStr">
+      <c r="AE18" s="2" t="inlineStr">
         <is>
           <t>UBER-NATURAL_DISASTER-001</t>
         </is>
       </c>
-      <c r="AF18" s="3" t="inlineStr"/>
-      <c r="AG18" s="3" t="inlineStr"/>
-      <c r="AH18" s="3" t="inlineStr"/>
-      <c r="AI18" s="3" t="inlineStr"/>
-      <c r="AJ18" s="3" t="inlineStr"/>
-      <c r="AK18" s="3" t="inlineStr"/>
-      <c r="AL18" s="3" t="inlineStr"/>
-      <c r="AM18" s="3" t="inlineStr"/>
-      <c r="AN18" s="3" t="inlineStr"/>
-      <c r="AO18" s="3" t="inlineStr"/>
-      <c r="AP18" s="3" t="inlineStr"/>
-      <c r="AQ18" s="3" t="inlineStr"/>
-      <c r="AR18" s="3" t="inlineStr"/>
-      <c r="AS18" s="3" t="inlineStr"/>
-      <c r="AT18" s="3" t="inlineStr"/>
-      <c r="AU18" s="3" t="inlineStr"/>
-      <c r="AV18" s="3" t="inlineStr"/>
-      <c r="AW18" s="3" t="inlineStr">
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr"/>
+      <c r="AK18" s="2" t="inlineStr"/>
+      <c r="AL18" s="2" t="inlineStr"/>
+      <c r="AM18" s="2" t="inlineStr"/>
+      <c r="AN18" s="2" t="inlineStr"/>
+      <c r="AO18" s="2" t="inlineStr"/>
+      <c r="AP18" s="2" t="inlineStr"/>
+      <c r="AQ18" s="2" t="inlineStr"/>
+      <c r="AR18" s="2" t="inlineStr"/>
+      <c r="AS18" s="2" t="inlineStr"/>
+      <c r="AT18" s="2" t="inlineStr"/>
+      <c r="AU18" s="2" t="inlineStr"/>
+      <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX18" s="3" t="inlineStr"/>
-      <c r="AY18" s="3" t="inlineStr"/>
-      <c r="AZ18" s="3" t="inlineStr"/>
-      <c r="BA18" s="3" t="inlineStr"/>
-      <c r="BB18" s="3" t="inlineStr">
+      <c r="AX18" s="2" t="inlineStr"/>
+      <c r="AY18" s="2" t="inlineStr"/>
+      <c r="AZ18" s="2" t="inlineStr"/>
+      <c r="BA18" s="2" t="inlineStr"/>
+      <c r="BB18" s="2" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="BC18" s="3" t="inlineStr">
+      <c r="BC18" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD18" s="3" t="inlineStr"/>
-      <c r="BE18" s="3" t="inlineStr">
+      <c r="BD18" s="2" t="inlineStr"/>
+      <c r="BE18" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF18" s="3" t="inlineStr">
+      <c r="BF18" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG18" s="3" t="inlineStr">
+      <c r="BG18" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH18" s="3" t="inlineStr"/>
+      <c r="BH18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr"/>
+      <c r="BJ18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr"/>
+      <c r="BL18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>NXPI</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>NXP Semiconductors</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>2026-10-10T00:12:20+08:00</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>NXP Semiconductors (NXPI) Stock May Be Near Fair Value After Citi Downgrade</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0.868</t>
         </is>
       </c>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="inlineStr"/>
-      <c r="R19" s="3" t="inlineStr"/>
-      <c r="S19" s="3" t="inlineStr"/>
-      <c r="T19" s="3" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U19" s="3" t="inlineStr">
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQU0RuWl9yU3BGM3hHN2VhcC1kYkM4cm42TnJxNzBKU1pfX3UyaW1KeEUyYWZiYmprRE9kelhoazJJUEExTVdEcGRjMlFUR28zLXI5OW8xUnhQcFdUWDRUTmEzb1RuU21jMktHSjRLVXVtc0QzQmNrbThaRFo0NVVzMDFLQlVickNFeGxNQkVpSVctM2Q3aF9xQW5KSDE0bGM?oc=5</t>
         </is>
       </c>
-      <c r="V19" s="3" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W19" s="3" t="inlineStr"/>
-      <c r="X19" s="3" t="inlineStr">
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
+      <c r="Y19" s="2" t="inlineStr">
         <is>
           <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
-      <c r="Z19" s="3" t="inlineStr">
+      <c r="Z19" s="2" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
       </c>
-      <c r="AA19" s="3" t="inlineStr">
+      <c r="AA19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB19" s="3" t="inlineStr"/>
-      <c r="AC19" s="3" t="inlineStr">
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
         <is>
           <t>47225f542f5d88e2220c7126</t>
         </is>
       </c>
-      <c r="AD19" s="3" t="inlineStr">
+      <c r="AD19" s="2" t="inlineStr">
         <is>
           <t>426f38508bc8a634e9067ab5</t>
         </is>
       </c>
-      <c r="AE19" s="3" t="inlineStr">
+      <c r="AE19" s="2" t="inlineStr">
         <is>
           <t>NXPI-ANALYST_DOWNGRADE-001</t>
         </is>
       </c>
-      <c r="AF19" s="3" t="inlineStr"/>
-      <c r="AG19" s="3" t="inlineStr"/>
-      <c r="AH19" s="3" t="inlineStr"/>
-      <c r="AI19" s="3" t="inlineStr"/>
-      <c r="AJ19" s="3" t="inlineStr"/>
-      <c r="AK19" s="3" t="inlineStr"/>
-      <c r="AL19" s="3" t="inlineStr"/>
-      <c r="AM19" s="3" t="inlineStr"/>
-      <c r="AN19" s="3" t="inlineStr"/>
-      <c r="AO19" s="3" t="inlineStr"/>
-      <c r="AP19" s="3" t="inlineStr"/>
-      <c r="AQ19" s="3" t="inlineStr"/>
-      <c r="AR19" s="3" t="inlineStr"/>
-      <c r="AS19" s="3" t="inlineStr"/>
-      <c r="AT19" s="3" t="inlineStr"/>
-      <c r="AU19" s="3" t="inlineStr"/>
-      <c r="AV19" s="3" t="inlineStr"/>
-      <c r="AW19" s="3" t="inlineStr"/>
-      <c r="AX19" s="3" t="inlineStr"/>
-      <c r="AY19" s="3" t="inlineStr"/>
-      <c r="AZ19" s="3" t="inlineStr"/>
-      <c r="BA19" s="3" t="inlineStr"/>
-      <c r="BB19" s="3" t="inlineStr">
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AI19" s="2" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr"/>
+      <c r="AK19" s="2" t="inlineStr"/>
+      <c r="AL19" s="2" t="inlineStr"/>
+      <c r="AM19" s="2" t="inlineStr"/>
+      <c r="AN19" s="2" t="inlineStr"/>
+      <c r="AO19" s="2" t="inlineStr"/>
+      <c r="AP19" s="2" t="inlineStr"/>
+      <c r="AQ19" s="2" t="inlineStr"/>
+      <c r="AR19" s="2" t="inlineStr"/>
+      <c r="AS19" s="2" t="inlineStr"/>
+      <c r="AT19" s="2" t="inlineStr"/>
+      <c r="AU19" s="2" t="inlineStr"/>
+      <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" s="2" t="inlineStr"/>
+      <c r="AX19" s="2" t="inlineStr"/>
+      <c r="AY19" s="2" t="inlineStr"/>
+      <c r="AZ19" s="2" t="inlineStr"/>
+      <c r="BA19" s="2" t="inlineStr"/>
+      <c r="BB19" s="2" t="inlineStr">
         <is>
           <t>NXPI</t>
         </is>
       </c>
-      <c r="BC19" s="3" t="inlineStr">
+      <c r="BC19" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD19" s="3" t="inlineStr"/>
-      <c r="BE19" s="3" t="inlineStr">
+      <c r="BD19" s="2" t="inlineStr"/>
+      <c r="BE19" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF19" s="3" t="inlineStr"/>
-      <c r="BG19" s="3" t="inlineStr">
+      <c r="BF19" s="2" t="inlineStr"/>
+      <c r="BG19" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH19" s="3" t="inlineStr"/>
+      <c r="BH19" s="2" t="inlineStr"/>
+      <c r="BI19" s="2" t="inlineStr"/>
+      <c r="BJ19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr"/>
+      <c r="BL19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Uber Technologies, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>2026-10-10T00:06:05+08:00</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Third bellwether trial in Uber sexual assault MDL ends in settlement</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>'-0.351</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr"/>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWGtZUGNaMnFFY0V1M0NCdFQyVXlfS2ZXQW5XbFoyVnF4YU5ia1pRQWhGcFdfOU5SWVpqNmRoWWJpN1FESENHb1JPb0QyMDFubWdmSC1GX3NWT2llcGZZMmhmV2xIcjVwZm5HSFdUTTk4TVBWcGhkSGdpd0FaR2xNSW1ISGRiWk5pVFpDdU5NTXQ2MDNuVXhRc0w1SmxESHNuVDVka3FEYU9fRHI2SVgtMmFIeWY3UkxHNVVYTmptbWxxQnlwWDhnRmdR?oc=5</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>Top Class Actions</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr"/>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>7b0b5b2af1f8434087e3615ceb30ec6d</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>c83927bfedbdfece350cf8e2</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr">
+        <is>
+          <t>b7e8d84e51baaa871fc4f876</t>
+        </is>
+      </c>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>UBER-REGULATORY_PENALTY-001</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr"/>
+      <c r="AG20" s="3" t="inlineStr"/>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr"/>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr"/>
+      <c r="AM20" s="3" t="inlineStr"/>
+      <c r="AN20" s="3" t="inlineStr"/>
+      <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>'-0.351</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="2" t="inlineStr"/>
-      <c r="S20" s="2" t="inlineStr"/>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWGtZUGNaMnFFY0V1M0NCdFQyVXlfS2ZXQW5XbFoyVnF4YU5ia1pRQWhGcFdfOU5SWVpqNmRoWWJpN1FESENHb1JPb0QyMDFubWdmSC1GX3NWT2llcGZZMmhmV2xIcjVwZm5HSFdUTTk4TVBWcGhkSGdpd0FaR2xNSW1ISGRiWk5pVFpDdU5NTXQ2MDNuVXhRc0w1SmxESHNuVDVka3FEYU9fRHI2SVgtMmFIeWY3UkxHNVVYTmptbWxxQnlwWDhnRmdR?oc=5</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Top Class Actions</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr"/>
-      <c r="X20" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y20" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z20" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
-      <c r="AC20" s="2" t="inlineStr">
-        <is>
-          <t>c83927bfedbdfece350cf8e2</t>
-        </is>
-      </c>
-      <c r="AD20" s="2" t="inlineStr">
-        <is>
-          <t>b7e8d84e51baaa871fc4f876</t>
-        </is>
-      </c>
-      <c r="AE20" s="2" t="inlineStr">
-        <is>
-          <t>UBER-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF20" s="2" t="inlineStr"/>
-      <c r="AG20" s="2" t="inlineStr"/>
-      <c r="AH20" s="2" t="inlineStr"/>
-      <c r="AI20" s="2" t="inlineStr"/>
-      <c r="AJ20" s="2" t="inlineStr"/>
-      <c r="AK20" s="2" t="inlineStr"/>
-      <c r="AL20" s="2" t="inlineStr"/>
-      <c r="AM20" s="2" t="inlineStr"/>
-      <c r="AN20" s="2" t="inlineStr"/>
-      <c r="AO20" s="2" t="inlineStr"/>
-      <c r="AP20" s="2" t="inlineStr"/>
-      <c r="AQ20" s="2" t="inlineStr"/>
-      <c r="AR20" s="2" t="inlineStr"/>
-      <c r="AS20" s="2" t="inlineStr"/>
-      <c r="AT20" s="2" t="inlineStr"/>
-      <c r="AU20" s="2" t="inlineStr"/>
-      <c r="AV20" s="2" t="inlineStr"/>
-      <c r="AW20" s="2" t="inlineStr">
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr"/>
+      <c r="AS20" s="3" t="inlineStr"/>
+      <c r="AT20" s="3" t="inlineStr"/>
+      <c r="AU20" s="3" t="inlineStr"/>
+      <c r="AV20" s="3" t="inlineStr"/>
+      <c r="AW20" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX20" s="2" t="inlineStr"/>
-      <c r="AY20" s="2" t="inlineStr"/>
-      <c r="AZ20" s="2" t="inlineStr"/>
-      <c r="BA20" s="2" t="inlineStr"/>
-      <c r="BB20" s="2" t="inlineStr">
+      <c r="AX20" s="3" t="inlineStr"/>
+      <c r="AY20" s="3" t="inlineStr"/>
+      <c r="AZ20" s="3" t="inlineStr"/>
+      <c r="BA20" s="3" t="inlineStr"/>
+      <c r="BB20" s="3" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="BC20" s="2" t="inlineStr">
+      <c r="BC20" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD20" s="2" t="inlineStr"/>
-      <c r="BE20" s="2" t="inlineStr">
+      <c r="BD20" s="3" t="inlineStr"/>
+      <c r="BE20" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF20" s="2" t="inlineStr">
+      <c r="BF20" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG20" s="2" t="inlineStr">
+      <c r="BG20" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH20" s="2" t="inlineStr"/>
+      <c r="BH20" s="3" t="inlineStr"/>
+      <c r="BI20" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ20" s="3" t="inlineStr"/>
+      <c r="BK20" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH20"/>
+  <autoFilter ref="A1:BL20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4088,7 +4260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4151,6 +4323,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4454,535 +4630,235 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>WMT</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Walmart Inc.</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-10T23:03:24+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Tariff refund class action lawsuits target Walmart, Puma, others</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10T00:06:05+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Third bellwether trial in Uber sexual assault MDL ends in settlement</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>重大訴訟</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>'-0.351</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWGtZUGNaMnFFY0V1M0NCdFQyVXlfS2ZXQW5XbFoyVnF4YU5ia1pRQWhGcFdfOU5SWVpqNmRoWWJpN1FESENHb1JPb0QyMDFubWdmSC1GX3NWT2llcGZZMmhmV2xIcjVwZm5HSFdUTTk4TVBWcGhkSGdpd0FaR2xNSW1ISGRiWk5pVFpDdU5NTXQ2MDNuVXhRc0w1SmxESHNuVDVka3FEYU9fRHI2SVgtMmFIeWY3UkxHNVVYTmptbWxxQnlwWDhnRmdR?oc=5</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>Top Class Actions</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr"/>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>7b0b5b2af1f8434087e3615ceb30ec6d</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>c83927bfedbdfece350cf8e2</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
+          <t>b7e8d84e51baaa871fc4f876</t>
+        </is>
+      </c>
+      <c r="AE2" s="3" t="inlineStr">
+        <is>
+          <t>UBER-REGULATORY_PENALTY-001</t>
+        </is>
+      </c>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" s="3" t="inlineStr"/>
+      <c r="AI2" s="3" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" s="3" t="inlineStr"/>
+      <c r="AM2" s="3" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>'-0.426</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNQ0I4VVY3Z0sweHFPTEVjd1NVakpmYy1sdFhYMGJnSnNrVFF5YVQzX2V0akhEeFRwSFo2YWZaYS1iR3UxYzBwUEl5NWc1UHczQ0FGNzdOZGdPUmY1Zm4xVmYyLUpsS1RWX2RQTUtyRzBuMEdOTndyQ0ZLaEo1bVRCMUdWeVhyUzBWZnR2SnF6QnZHUHVOLXhEN1JaNkVfaHhUeWI0a1hpTFhpZTk5RThrblNSTGQwN1lZbWpBZ2Ewb1RUUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>Top Class Actions</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>94b9da2b8baf4ad0cc5a2b28</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>aed03c1292af01ec9e457a52</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr">
-        <is>
-          <t>WMT-MAJOR_LITIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>WMT</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
+      <c r="AP2" s="3" t="inlineStr"/>
+      <c r="AQ2" s="3" t="inlineStr"/>
+      <c r="AR2" s="3" t="inlineStr"/>
+      <c r="AS2" s="3" t="inlineStr"/>
+      <c r="AT2" s="3" t="inlineStr"/>
+      <c r="AU2" s="3" t="inlineStr"/>
+      <c r="AV2" s="3" t="inlineStr"/>
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX2" s="3" t="inlineStr"/>
+      <c r="AY2" s="3" t="inlineStr"/>
+      <c r="AZ2" s="3" t="inlineStr"/>
+      <c r="BA2" s="3" t="inlineStr"/>
+      <c r="BB2" s="3" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="BC2" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD2" s="2" t="inlineStr"/>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="2" t="inlineStr">
+      <c r="BD2" s="3" t="inlineStr"/>
+      <c r="BE2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG2" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-10T20:11:21+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Is Coinbase Global (COIN) Cheap As CFTC Approval Reshapes Its Valuation?</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>0.259</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxORmpmYzNtREFBc2xnZURoNGYxcm5rZExJX2FUa2d0WmU5akU1TjI2c04xU1ZSZnBkRDQwTVlxMkRrZ1NCbEs4YWJuMUZRbWRsSjlIamhENzJDUkp1TnVMOUtNYkdfMDN3MEtQTG9wbUJkUHBqUjJ0WFRfalFqMXFwbWpLRkVWZVZjajJMS1k3VURWbFh0RWttVEdtTXY?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>CFTC；FTC</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>a8c475715ee1d4253926397c</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>1dcf8943046a379290ed336b</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr">
-        <is>
-          <t>COIN-REGULATORY_INVESTIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr"/>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr"/>
-      <c r="AM3" s="2" t="inlineStr"/>
-      <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
-      <c r="AP3" s="2" t="inlineStr"/>
-      <c r="AQ3" s="2" t="inlineStr"/>
-      <c r="AR3" s="2" t="inlineStr"/>
-      <c r="AS3" s="2" t="inlineStr"/>
-      <c r="AT3" s="2" t="inlineStr"/>
-      <c r="AU3" s="2" t="inlineStr"/>
-      <c r="AV3" s="2" t="inlineStr"/>
-      <c r="AW3" s="2" t="inlineStr"/>
-      <c r="AX3" s="2" t="inlineStr"/>
-      <c r="AY3" s="2" t="inlineStr"/>
-      <c r="AZ3" s="2" t="inlineStr"/>
-      <c r="BA3" s="2" t="inlineStr"/>
-      <c r="BB3" s="2" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="BC3" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD3" s="2" t="inlineStr"/>
-      <c r="BE3" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF3" s="2" t="inlineStr"/>
-      <c r="BG3" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Uber Technologies, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-10T00:06:05+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Third bellwether trial in Uber sexual assault MDL ends in settlement</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>'-0.351</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWGtZUGNaMnFFY0V1M0NCdFQyVXlfS2ZXQW5XbFoyVnF4YU5ia1pRQWhGcFdfOU5SWVpqNmRoWWJpN1FESENHb1JPb0QyMDFubWdmSC1GX3NWT2llcGZZMmhmV2xIcjVwZm5HSFdUTTk4TVBWcGhkSGdpd0FaR2xNSW1ISGRiWk5pVFpDdU5NTXQ2MDNuVXhRc0w1SmxESHNuVDVka3FEYU9fRHI2SVgtMmFIeWY3UkxHNVVYTmptbWxxQnlwWDhnRmdR?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Top Class Actions</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>c83927bfedbdfece350cf8e2</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>b7e8d84e51baaa871fc4f876</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr">
-        <is>
-          <t>UBER-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF4" s="2" t="inlineStr"/>
-      <c r="AG4" s="2" t="inlineStr"/>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr"/>
-      <c r="AM4" s="2" t="inlineStr"/>
-      <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
-      <c r="AP4" s="2" t="inlineStr"/>
-      <c r="AQ4" s="2" t="inlineStr"/>
-      <c r="AR4" s="2" t="inlineStr"/>
-      <c r="AS4" s="2" t="inlineStr"/>
-      <c r="AT4" s="2" t="inlineStr"/>
-      <c r="AU4" s="2" t="inlineStr"/>
-      <c r="AV4" s="2" t="inlineStr"/>
-      <c r="AW4" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX4" s="2" t="inlineStr"/>
-      <c r="AY4" s="2" t="inlineStr"/>
-      <c r="AZ4" s="2" t="inlineStr"/>
-      <c r="BA4" s="2" t="inlineStr"/>
-      <c r="BB4" s="2" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="BC4" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD4" s="2" t="inlineStr"/>
-      <c r="BE4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG4" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH4"/>
+  <autoFilter ref="A1:BL2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4993,7 +4869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5056,6 +4932,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5359,9 +5239,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5372,7 +5272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5435,6 +5335,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5738,9 +5642,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5751,7 +5675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5801,477 +5725,768 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>ticker-audit-20261024-081549</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>ticker-audit</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>daily-2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="3" t="n">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr"/>
-      <c r="N2" s="3" t="inlineStr"/>
-      <c r="O2" s="3" t="inlineStr"/>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr"/>
-      <c r="V2" s="3" t="inlineStr"/>
-      <c r="W2" s="3" t="inlineStr"/>
-      <c r="X2" s="3" t="inlineStr"/>
-      <c r="Y2" s="3" t="inlineStr"/>
-      <c r="Z2" s="3" t="inlineStr"/>
-      <c r="AA2" s="3" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>daily-2026-10-25</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="b">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="Q3" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="R3" s="3" t="n">
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="U3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>2089</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="n">
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="Z3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="V3" s="2" t="n">
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>daily-2026-10-24</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="n">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>3802</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ticker-audit-20261024-081549</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ticker-audit</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:11.949238+08:00</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:18.833437+08:00</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="n">
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="n">
+      <c r="M8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="b">
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="R5" s="3" t="n">
+      <c r="V8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="3" t="n">
+      <c r="W8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-10-10.xlsx
+++ b/news_daily/2026-10-10.xlsx
@@ -1086,28 +1086,32 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1147,7 +1151,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -1160,7 +1164,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>f340e26eb94b419490c7d6cdc1eff91a</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>f0f77ba8cc3347d3fb4b041b</t>
@@ -1185,7 +1193,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -1221,10 +1233,22 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1458,28 +1482,32 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1519,7 +1547,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1532,7 +1560,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>a788b78ec95b4afb91442068f197da1d</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>a03d519accae46b313527dd7</t>
@@ -1557,7 +1589,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -1601,10 +1637,22 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
-      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1640,28 +1688,32 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1701,7 +1753,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1714,7 +1766,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>0cf939db9b6e4b648b986f8e1023049e</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>9b74328762308f6419882e27</t>
@@ -1739,7 +1795,11 @@
       <c r="AL6" s="2" t="inlineStr"/>
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="2" t="inlineStr"/>
       <c r="AQ6" s="2" t="inlineStr"/>
       <c r="AR6" s="2" t="inlineStr"/>
@@ -1783,10 +1843,22 @@
         </is>
       </c>
       <c r="BH6" s="2" t="inlineStr"/>
-      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ6" s="2" t="inlineStr"/>
-      <c r="BK6" s="2" t="inlineStr"/>
-      <c r="BL6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1822,28 +1894,32 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1883,7 +1959,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1896,7 +1972,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>7628bceeb5ec4996ae7a07ab71698468</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>649824e2d268d058f0ad4c21</t>
@@ -1921,7 +2001,11 @@
       <c r="AL7" s="2" t="inlineStr"/>
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="2" t="inlineStr"/>
       <c r="AQ7" s="2" t="inlineStr"/>
       <c r="AR7" s="2" t="inlineStr"/>
@@ -1965,10 +2049,22 @@
         </is>
       </c>
       <c r="BH7" s="2" t="inlineStr"/>
-      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ7" s="2" t="inlineStr"/>
-      <c r="BK7" s="2" t="inlineStr"/>
-      <c r="BL7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2004,28 +2100,32 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2065,7 +2165,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -2078,7 +2178,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>d6167fc8b8ae4e0682a144462821311a</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>6d237aea5670dbfdca2da9bf</t>
@@ -2103,7 +2207,11 @@
       <c r="AL8" s="2" t="inlineStr"/>
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="2" t="inlineStr"/>
       <c r="AQ8" s="2" t="inlineStr"/>
       <c r="AR8" s="2" t="inlineStr"/>
@@ -2147,10 +2255,22 @@
         </is>
       </c>
       <c r="BH8" s="2" t="inlineStr"/>
-      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ8" s="2" t="inlineStr"/>
-      <c r="BK8" s="2" t="inlineStr"/>
-      <c r="BL8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2518,28 +2638,32 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2579,7 +2703,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -2592,7 +2716,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>fda43ea2a755482e99a8b021a41473ab</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>fc1a753b967db841d5bdb4ef</t>
@@ -2617,7 +2745,11 @@
       <c r="AL11" s="2" t="inlineStr"/>
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="2" t="inlineStr"/>
       <c r="AQ11" s="2" t="inlineStr"/>
       <c r="AR11" s="2" t="inlineStr"/>
@@ -2661,10 +2793,22 @@
         </is>
       </c>
       <c r="BH11" s="2" t="inlineStr"/>
-      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ11" s="2" t="inlineStr"/>
-      <c r="BK11" s="2" t="inlineStr"/>
-      <c r="BL11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2700,28 +2844,32 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2761,7 +2909,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -2774,7 +2922,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>6658ab8542b14970a0e309e2e95bf4c5</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
           <t>0d0608c617221536e2d0e989</t>
@@ -2799,7 +2951,11 @@
       <c r="AL12" s="2" t="inlineStr"/>
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="2" t="inlineStr"/>
       <c r="AQ12" s="2" t="inlineStr"/>
       <c r="AR12" s="2" t="inlineStr"/>
@@ -2843,10 +2999,22 @@
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr"/>
-      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ12" s="2" t="inlineStr"/>
-      <c r="BK12" s="2" t="inlineStr"/>
-      <c r="BL12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2882,28 +3050,32 @@
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2943,7 +3115,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2956,7 +3128,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>d2beb43f688f4bb38adb6d177c1d1426</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
           <t>0fc35c0667c313f8102e2fee</t>
@@ -2981,7 +3157,11 @@
       <c r="AL13" s="2" t="inlineStr"/>
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr"/>
-      <c r="AO13" s="2" t="inlineStr"/>
+      <c r="AO13" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="2" t="inlineStr"/>
       <c r="AQ13" s="2" t="inlineStr"/>
       <c r="AR13" s="2" t="inlineStr"/>
@@ -3017,10 +3197,22 @@
         </is>
       </c>
       <c r="BH13" s="2" t="inlineStr"/>
-      <c r="BI13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ13" s="2" t="inlineStr"/>
-      <c r="BK13" s="2" t="inlineStr"/>
-      <c r="BL13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3056,28 +3248,32 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3117,7 +3313,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -3130,7 +3326,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>e3f27a52d249458694c6214dbeddc9a1</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
           <t>772cf080a9a1a672a6d4f5f6</t>
@@ -3155,7 +3355,11 @@
       <c r="AL14" s="2" t="inlineStr"/>
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr"/>
-      <c r="AO14" s="2" t="inlineStr"/>
+      <c r="AO14" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP14" s="2" t="inlineStr"/>
       <c r="AQ14" s="2" t="inlineStr"/>
       <c r="AR14" s="2" t="inlineStr"/>
@@ -3199,10 +3403,22 @@
         </is>
       </c>
       <c r="BH14" s="2" t="inlineStr"/>
-      <c r="BI14" s="2" t="inlineStr"/>
+      <c r="BI14" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ14" s="2" t="inlineStr"/>
-      <c r="BK14" s="2" t="inlineStr"/>
-      <c r="BL14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3720,28 +3936,32 @@
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -3781,7 +4001,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -3794,7 +4014,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>901914b1d55d4ee1bb2f1d27e81d6eaa</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>3221cb812084a113528df1ad</t>
@@ -3819,7 +4043,11 @@
       <c r="AL18" s="2" t="inlineStr"/>
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr"/>
-      <c r="AO18" s="2" t="inlineStr"/>
+      <c r="AO18" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="2" t="inlineStr"/>
       <c r="AQ18" s="2" t="inlineStr"/>
       <c r="AR18" s="2" t="inlineStr"/>
@@ -3863,10 +4091,22 @@
         </is>
       </c>
       <c r="BH18" s="2" t="inlineStr"/>
-      <c r="BI18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ18" s="2" t="inlineStr"/>
-      <c r="BK18" s="2" t="inlineStr"/>
-      <c r="BL18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3917,13 +4157,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -3976,7 +4220,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>226dea85ae5a43f387a9373cdfd154d2</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
           <t>47225f542f5d88e2220c7126</t>
@@ -4001,7 +4249,11 @@
       <c r="AL19" s="2" t="inlineStr"/>
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr"/>
-      <c r="AO19" s="2" t="inlineStr"/>
+      <c r="AO19" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP19" s="2" t="inlineStr"/>
       <c r="AQ19" s="2" t="inlineStr"/>
       <c r="AR19" s="2" t="inlineStr"/>
@@ -4039,8 +4291,16 @@
       <c r="BH19" s="2" t="inlineStr"/>
       <c r="BI19" s="2" t="inlineStr"/>
       <c r="BJ19" s="2" t="inlineStr"/>
-      <c r="BK19" s="2" t="inlineStr"/>
-      <c r="BL19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">

--- a/news_daily/2026-10-10.xlsx
+++ b/news_daily/2026-10-10.xlsx
@@ -2324,7 +2324,11 @@
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -2380,7 +2384,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>7afaf28a7f384df5a2d24fa8274ac527</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>9be7f426b71d4c91b7ba4737</t>
@@ -2405,7 +2413,11 @@
       <c r="AL9" s="2" t="inlineStr"/>
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="2" t="inlineStr"/>
       <c r="AQ9" s="2" t="inlineStr"/>
       <c r="AR9" s="2" t="inlineStr"/>
@@ -2435,8 +2447,16 @@
       </c>
       <c r="BI9" s="2" t="inlineStr"/>
       <c r="BJ9" s="2" t="inlineStr"/>
-      <c r="BK9" s="2" t="inlineStr"/>
-      <c r="BL9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:26:33.476936+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2490,7 +2510,11 @@
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -2546,7 +2570,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>0b8869820ce1446a8be2b07bfcdf7f9d</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>9be7f426b71d4c91b7ba4737</t>
@@ -2571,7 +2599,11 @@
       <c r="AL10" s="2" t="inlineStr"/>
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="2" t="inlineStr"/>
       <c r="AQ10" s="2" t="inlineStr"/>
       <c r="AR10" s="2" t="inlineStr"/>
@@ -2601,8 +2633,16 @@
       </c>
       <c r="BI10" s="2" t="inlineStr"/>
       <c r="BJ10" s="2" t="inlineStr"/>
-      <c r="BK10" s="2" t="inlineStr"/>
-      <c r="BL10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:26:33.476936+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3472,7 +3512,11 @@
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -3528,7 +3572,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>a16f5e7aab544b2b949714c0e556694e</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
           <t>2d8847c76339218fad2c6db6</t>
@@ -3553,7 +3601,11 @@
       <c r="AL15" s="2" t="inlineStr"/>
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr"/>
-      <c r="AO15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP15" s="2" t="inlineStr"/>
       <c r="AQ15" s="2" t="inlineStr"/>
       <c r="AR15" s="2" t="inlineStr"/>
@@ -3579,8 +3631,16 @@
       <c r="BH15" s="2" t="inlineStr"/>
       <c r="BI15" s="2" t="inlineStr"/>
       <c r="BJ15" s="2" t="inlineStr"/>
-      <c r="BK15" s="2" t="inlineStr"/>
-      <c r="BL15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:26:33.476936+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3634,7 +3694,11 @@
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -3690,7 +3754,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>cc01051583c242d48f19e5caca72c6b8</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
           <t>2d8847c76339218fad2c6db6</t>
@@ -3715,7 +3783,11 @@
       <c r="AL16" s="2" t="inlineStr"/>
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr"/>
-      <c r="AO16" s="2" t="inlineStr"/>
+      <c r="AO16" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="2" t="inlineStr"/>
       <c r="AQ16" s="2" t="inlineStr"/>
       <c r="AR16" s="2" t="inlineStr"/>
@@ -3741,8 +3813,16 @@
       <c r="BH16" s="2" t="inlineStr"/>
       <c r="BI16" s="2" t="inlineStr"/>
       <c r="BJ16" s="2" t="inlineStr"/>
-      <c r="BK16" s="2" t="inlineStr"/>
-      <c r="BL16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:26:33.476936+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3776,10 +3856,14 @@
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>一般公司更新</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3792,7 +3876,11 @@
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -3835,7 +3923,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>BANKRUPTCY</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -3848,7 +3936,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>3624e0a0bf974faea70ae4e4821195e8</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
           <t>4654f2f090918d96da79b5df</t>
@@ -3873,7 +3965,11 @@
       <c r="AL17" s="2" t="inlineStr"/>
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr"/>
-      <c r="AO17" s="2" t="inlineStr"/>
+      <c r="AO17" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP17" s="2" t="inlineStr"/>
       <c r="AQ17" s="2" t="inlineStr"/>
       <c r="AR17" s="2" t="inlineStr"/>
@@ -3897,10 +3993,22 @@
       <c r="BF17" s="2" t="inlineStr"/>
       <c r="BG17" s="2" t="inlineStr"/>
       <c r="BH17" s="2" t="inlineStr"/>
-      <c r="BI17" s="2" t="inlineStr"/>
+      <c r="BI17" s="2" t="inlineStr">
+        <is>
+          <t>Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ17" s="2" t="inlineStr"/>
-      <c r="BK17" s="2" t="inlineStr"/>
-      <c r="BL17" s="2" t="inlineStr"/>
+      <c r="BK17" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:26:33.476936+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
